--- a/patient_registration_form_templates/024_remote_patient_monitoring_study_registration--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/024_remote_patient_monitoring_study_registration--patient_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_aware_of_the_purpose_and_risks_associated_with_this_study.'}</t>
+          <t>i_am_aware_of_the_purpose_and_risks_associated_with_this_study.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'I am aware of the purpose and risks associated with this study.'}</t>
+          <t>I am aware of the purpose and risks associated with this study.</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_read_and_understand_the_information_provided_above.'}</t>
+          <t>i_have_read_and_understand_the_information_provided_above.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'I have read and understand the information provided above.'}</t>
+          <t>I have read and understand the information provided above.</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'child'}</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Child'}</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'sibling'}</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Sibling'}</t>
+          <t>Sibling</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
